--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487617_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487617_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0503</v>
+        <v>0.3923</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9555</v>
+        <v>-1.3954</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0058</v>
+        <v>1.7877</v>
       </c>
       <c r="G2" t="n">
         <v>-1.1127</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8495</v>
+        <v>0.1915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6202</v>
+        <v>0.1803</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2293</v>
+        <v>0.0112</v>
       </c>
       <c r="V2" t="n">
         <v>0.5373</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.0808</v>
+        <v>-1.4411</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1699</v>
+        <v>-0.302</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9109</v>
+        <v>-1.1391</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0648</v>
+        <v>-4.0129</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2809</v>
+        <v>-0.2719</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3458</v>
+        <v>-3.741</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0916</v>
+        <v>-1.6648</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2431</v>
+        <v>0.2966</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3347</v>
+        <v>-1.9614</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0267</v>
+        <v>-2.3481</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0379</v>
+        <v>-0.5685</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0111</v>
+        <v>-1.7796</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1756</v>
+        <v>-0.0208</v>
       </c>
       <c r="T3" t="n">
-        <v>0.074</v>
+        <v>-0.0954</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2496</v>
+        <v>0.0746</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4522</v>
+        <v>0.8462</v>
       </c>
       <c r="W3" t="n">
-        <v>1.788</v>
+        <v>1.4582</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2403</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.1378</v>
+        <v>-1.6769</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.0902</v>
+        <v>-3.6292</v>
       </c>
       <c r="F4" t="n">
         <v>1.9523</v>
@@ -766,10 +766,10 @@
         <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0307</v>
+        <v>-0.5698</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8356</v>
+        <v>-0.3746</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1951</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1615</v>
+        <v>-2.2021</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2279</v>
+        <v>-1.2094</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0664</v>
+        <v>-0.9927</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.22</v>
+        <v>-1.0648</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1977</v>
+        <v>0.2809</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0223</v>
+        <v>-1.3458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1153</v>
+        <v>-1.0916</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1153</v>
+        <v>0.2431</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.3347</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3354</v>
+        <v>0.0267</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3131</v>
+        <v>0.0379</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0223</v>
+        <v>-0.0111</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0415</v>
+        <v>-0.2969</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2568</v>
+        <v>0.0345</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2983</v>
+        <v>-0.3314</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.288</v>
+        <v>-0.4522</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6597</v>
+        <v>1.788</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6283</v>
+        <v>-2.2403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3237</v>
+        <v>-2.3651</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1027</v>
+        <v>-2.5677</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2209</v>
+        <v>0.2026</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.0129</v>
+        <v>-0.22</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2719</v>
+        <v>-0.1977</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.741</v>
+        <v>-0.0223</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6648</v>
+        <v>0.1153</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2966</v>
+        <v>0.1153</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9614</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3481</v>
+        <v>-0.3354</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5685</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7796</v>
+        <v>-0.0223</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9033</v>
+        <v>-0.2451</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.083</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0072</v>
+        <v>-0.162</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8462</v>
+        <v>-2.288</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4582</v>
+        <v>-0.6597</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6119</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8113</v>
+        <v>-2.6177</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2745</v>
+        <v>-1.6483</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5368</v>
+        <v>-0.9694</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4158</v>
+        <v>-2.5833</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5489</v>
+        <v>1.2968</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8669</v>
+        <v>-3.88</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9398</v>
+        <v>0.0489</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9804</v>
+        <v>2.0103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>-1.9614</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.476</v>
+        <v>-2.6321</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5685</v>
+        <v>-0.7135</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9075</v>
+        <v>-1.9187</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3881</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5358</v>
+        <v>-0.0179</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9549</v>
+        <v>-0.2165</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.419</v>
+        <v>0.1985</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3194</v>
+        <v>2.1179</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.3194</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.255</v>
+        <v>-3.6346</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4491</v>
+        <v>-1.8261</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-1.8084</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5833</v>
+        <v>-1.5314</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2968</v>
+        <v>0.3188</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.88</v>
+        <v>-1.8502</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0489</v>
+        <v>0.0104</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0103</v>
+        <v>0.7538</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9614</v>
+        <v>-0.7435</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6321</v>
+        <v>-1.5417</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7135</v>
+        <v>-0.435</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9187</v>
+        <v>-1.1067</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6552</v>
+        <v>-0.6853</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0173</v>
+        <v>-0.5081</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3621</v>
+        <v>-0.1772</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1179</v>
+        <v>-1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4</v>
+        <v>0.6119</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4271</v>
+        <v>-4.0219</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0778</v>
+        <v>-2.6759</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.5049</v>
+        <v>-1.346</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3725</v>
+        <v>-3.4158</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7085</v>
+        <v>-1.5489</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6639</v>
+        <v>-1.8669</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0481</v>
+        <v>-0.9398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0659</v>
+        <v>-0.9804</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0178</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4206</v>
+        <v>-2.476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7744</v>
+        <v>-0.5685</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6462</v>
+        <v>-1.9075</v>
       </c>
       <c r="P9" t="n">
         <v>0.3881</v>
@@ -1156,28 +1156,28 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3349</v>
+        <v>0.3252</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1058</v>
+        <v>0.5535</v>
       </c>
       <c r="U9" t="n">
-        <v>0.229</v>
+        <v>-0.2282</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.7776</v>
+        <v>-1.3194</v>
       </c>
       <c r="W9" t="n">
-        <v>0.894</v>
+        <v>-1.3194</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9804</v>
+        <v>-4.3369</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2265</v>
+        <v>0.277</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7539</v>
+        <v>-4.614</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5314</v>
+        <v>-2.3725</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3188</v>
+        <v>-0.7085</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8502</v>
+        <v>-1.6639</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0104</v>
+        <v>0.0481</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7538</v>
+        <v>0.0659</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7435</v>
+        <v>-0.0178</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5417</v>
+        <v>-2.4206</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.435</v>
+        <v>-0.7744</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1067</v>
+        <v>-1.6462</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0312</v>
+        <v>0.4251</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9085</v>
+        <v>0.305</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1227</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>-2.7776</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6119</v>
+        <v>0.894</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8358</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6178</v>
+        <v>-6.5384</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5065</v>
+        <v>-5.6451</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1113</v>
+        <v>-0.8933</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5566</v>
@@ -1312,13 +1312,13 @@
         <v>2.7164</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8791</v>
+        <v>-0.7997</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3078</v>
+        <v>-0.4464</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5713</v>
+        <v>-0.3533</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9582</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.7451</v>
+        <v>-28.4424</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.925</v>
+        <v>-20.6221</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.8201</v>
+        <v>-7.8203</v>
       </c>
       <c r="G12" t="n">
         <v>-23.2726</v>
@@ -1363,7 +1363,7 @@
         <v>-19.631</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.215800000000002</v>
+        <v>-9.2158</v>
       </c>
       <c r="K12" t="n">
         <v>0.7663</v>
@@ -1378,7 +1378,7 @@
         <v>-4.4079</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.648900000000001</v>
+        <v>-9.648899999999999</v>
       </c>
       <c r="P12" t="n">
         <v>1.9403</v>
@@ -1390,19 +1390,19 @@
         <v>18.4331</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9964</v>
+        <v>-1.6937</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9537000000000003</v>
+        <v>-0.6507000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0428</v>
+        <v>-1.0429</v>
       </c>
       <c r="V12" t="n">
         <v>-5.416399999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.737200000000001</v>
+        <v>5.7372</v>
       </c>
       <c r="X12" t="n">
         <v>-11.1536</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.375400000000001</v>
+        <v>7.3504</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4002</v>
+        <v>4.2991</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9752</v>
+        <v>3.0513</v>
       </c>
       <c r="G13" t="n">
         <v>4.5679</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3881</v>
+        <v>0.3631</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4087</v>
+        <v>0.3076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0206</v>
+        <v>0.0556</v>
       </c>
       <c r="V13" t="n">
         <v>3.3895</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2803</v>
+        <v>4.6498</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6844</v>
+        <v>0.3632</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5959</v>
+        <v>4.2867</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7201</v>
+        <v>1.5953</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6385</v>
+        <v>0.6377</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0816</v>
+        <v>0.9576</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2379</v>
+        <v>0.2283</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9516</v>
+        <v>0.0659</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2864</v>
+        <v>0.1624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4821</v>
+        <v>1.367</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3131</v>
+        <v>0.5718</v>
       </c>
       <c r="O14" t="n">
         <v>0.7952</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="R14" t="n">
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4542</v>
+        <v>0.5605</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0595</v>
+        <v>0.2408</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5137</v>
+        <v>0.3197</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3299</v>
+        <v>0.9418</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X14" t="n">
         <v>0.6597</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2706</v>
+        <v>4.3442</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0629</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2077</v>
+        <v>3.4596</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5953</v>
+        <v>2.7201</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6377</v>
+        <v>0.6385</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9576</v>
+        <v>2.0816</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2283</v>
+        <v>2.2379</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0659</v>
+        <v>0.9516</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1624</v>
+        <v>1.2864</v>
       </c>
       <c r="M15" t="n">
-        <v>1.367</v>
+        <v>0.4821</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5718</v>
+        <v>-0.3131</v>
       </c>
       <c r="O15" t="n">
         <v>0.7952</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3881</v>
+        <v>-1.1642</v>
       </c>
       <c r="R15" t="n">
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1813</v>
+        <v>0.5182</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0595</v>
+        <v>0.1407</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2407</v>
+        <v>0.3774</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9418</v>
+        <v>0.3299</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X15" t="n">
         <v>0.6597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5246</v>
+        <v>3.9123</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2886</v>
+        <v>2.1885</v>
       </c>
       <c r="F16" t="n">
-        <v>1.236</v>
+        <v>1.7237</v>
       </c>
       <c r="G16" t="n">
         <v>0.638</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5029</v>
+        <v>-0.1152</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1346</v>
+        <v>0.0345</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6375</v>
+        <v>-0.1497</v>
       </c>
       <c r="V16" t="n">
         <v>3.3895</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2688</v>
+        <v>2.5212</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2667</v>
+        <v>0.7672</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0022</v>
+        <v>1.7541</v>
       </c>
       <c r="G17" t="n">
         <v>0.204</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.229</v>
+        <v>0.4814</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7618</v>
+        <v>0.5137</v>
       </c>
       <c r="V17" t="n">
         <v>1.8358</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1471</v>
+        <v>2.1377</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6516</v>
+        <v>0.4514</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4954</v>
+        <v>1.6862</v>
       </c>
       <c r="G18" t="n">
         <v>3.0099</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>0.273</v>
+        <v>0.2636</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2434</v>
+        <v>0.0432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0296</v>
+        <v>0.2204</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5322</v>
+        <v>1.6835</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6791</v>
+        <v>-1.8793</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2113</v>
+        <v>3.5628</v>
       </c>
       <c r="G19" t="n">
         <v>0.7308</v>
@@ -1936,13 +1936,13 @@
         <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3641</v>
+        <v>0.5154</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4867</v>
+        <v>0.2865</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1227</v>
+        <v>0.2288</v>
       </c>
       <c r="V19" t="n">
         <v>1.6015</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2331</v>
+        <v>1.6095</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1771</v>
+        <v>1.4774</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0559</v>
+        <v>0.1321</v>
       </c>
       <c r="G20" t="n">
         <v>3.5673</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1283</v>
+        <v>0.2482</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1745</v>
+        <v>0.2507</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1371</v>
+        <v>1.3791</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2397</v>
+        <v>0.9394</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1025</v>
+        <v>0.4397</v>
       </c>
       <c r="G21" t="n">
         <v>3.9762</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>0.249</v>
+        <v>0.491</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6079</v>
+        <v>0.3076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3589</v>
+        <v>0.1834</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1179</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5094</v>
+        <v>0.5823</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2972</v>
+        <v>-0.1971</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8066</v>
+        <v>0.7793</v>
       </c>
       <c r="G22" t="n">
         <v>1.1949</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0906</v>
+        <v>0.1635</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1512</v>
+        <v>0.1239</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1689</v>
+        <v>0.2055</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.573</v>
+        <v>-0.1014</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4042</v>
+        <v>0.3069</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5713</v>
+        <v>-0.5032</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8633999999999999</v>
+        <v>-0.5437</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7079</v>
+        <v>0.0406</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3506</v>
+        <v>-0.602</v>
       </c>
       <c r="K23" t="n">
-        <v>1.31</v>
+        <v>0.0247</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0406</v>
+        <v>-0.6267</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2208</v>
+        <v>0.0989</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4466</v>
+        <v>-0.5685</v>
       </c>
       <c r="O23" t="n">
         <v>0.6673</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0837</v>
+        <v>-0.1152</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4116</v>
+        <v>-0.1113</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4953</v>
+        <v>-0.0039</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6597</v>
+        <v>0.0478</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3776</v>
+        <v>0.6119</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3645</v>
+        <v>-0.2957</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4017</v>
+        <v>-1.3729</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0372</v>
+        <v>1.0771</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5032</v>
+        <v>1.5713</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5437</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="I24" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.3506</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.0406</v>
       </c>
-      <c r="J24" t="n">
-        <v>-0.602</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-0.6267</v>
-      </c>
       <c r="M24" t="n">
-        <v>0.0989</v>
+        <v>0.2208</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5685</v>
+        <v>-0.4466</v>
       </c>
       <c r="O24" t="n">
         <v>0.6673</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6853</v>
+        <v>-0.0432</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4116</v>
+        <v>-0.2114</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2736</v>
+        <v>0.1683</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0478</v>
+        <v>-0.6597</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6119</v>
+        <v>-0.3776</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>28.7452</v>
+        <v>30.0798</v>
       </c>
       <c r="E25" t="n">
-        <v>7.820199999999998</v>
+        <v>7.820099999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>20.9251</v>
+        <v>22.2595</v>
       </c>
       <c r="G25" t="n">
         <v>23.2725</v>
       </c>
       <c r="H25" t="n">
-        <v>3.641300000000001</v>
+        <v>3.6413</v>
       </c>
       <c r="I25" t="n">
         <v>19.6311</v>
@@ -2380,7 +2380,7 @@
         <v>14.0568</v>
       </c>
       <c r="K25" t="n">
-        <v>4.407800000000001</v>
+        <v>4.4078</v>
       </c>
       <c r="L25" t="n">
         <v>9.649099999999999</v>
@@ -2404,13 +2404,13 @@
         <v>16.4927</v>
       </c>
       <c r="S25" t="n">
-        <v>1.996499999999999</v>
+        <v>3.3313</v>
       </c>
       <c r="T25" t="n">
         <v>1.0429</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9535</v>
+        <v>2.2883</v>
       </c>
       <c r="V25" t="n">
         <v>5.416399999999998</v>
